--- a/data/accessories.xlsx
+++ b/data/accessories.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Pictures\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{AA61A507-BC83-49E2-91C5-28D473B535B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B80BBCF9-B334-44DA-9412-A74E9D62D2F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{92D39A36-05D7-4D9B-8BB2-8A3D22F7C6C4}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="53">
   <si>
     <t>white</t>
   </si>
@@ -118,6 +118,81 @@
   </si>
   <si>
     <t>Focus Pen Pro</t>
+  </si>
+  <si>
+    <t>Cable</t>
+  </si>
+  <si>
+    <t>Usb to Lightning</t>
+  </si>
+  <si>
+    <t>C to Lightning</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C to C </t>
+  </si>
+  <si>
+    <t>MI</t>
+  </si>
+  <si>
+    <t>6A HYPERCHARGE</t>
+  </si>
+  <si>
+    <t>SONIC TYPE-C 2.0</t>
+  </si>
+  <si>
+    <t>IYNK C-C 60W 1M</t>
+  </si>
+  <si>
+    <t>silver,blue,orange</t>
+  </si>
+  <si>
+    <t>IYNK C-L 30W 1M</t>
+  </si>
+  <si>
+    <t>TUG A-C 6.5A 65W 1.2M</t>
+  </si>
+  <si>
+    <t xml:space="preserve">white </t>
+  </si>
+  <si>
+    <t>TUG C-C 5A 100W 1.2M</t>
+  </si>
+  <si>
+    <t>Smart Watch</t>
+  </si>
+  <si>
+    <t>Noise</t>
+  </si>
+  <si>
+    <t>JUNIOR EXPLORER 2</t>
+  </si>
+  <si>
+    <t>blue,pink</t>
+  </si>
+  <si>
+    <t>REDMI WATCH MOVE</t>
+  </si>
+  <si>
+    <t>gold,blue,black,silver</t>
+  </si>
+  <si>
+    <t>all models available</t>
+  </si>
+  <si>
+    <t>Inquire price</t>
+  </si>
+  <si>
+    <t>NOISEFIT VORTEX PLUS</t>
+  </si>
+  <si>
+    <t>COLORFIT PULSE 2 PRO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">silver </t>
+  </si>
+  <si>
+    <t>brown</t>
   </si>
 </sst>
 </file>
@@ -472,7 +547,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF37606E-F1B9-4EEF-A26B-A858B1111E90}">
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E30"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.7109375" customWidth="1"/>
@@ -500,104 +575,100 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>3</v>
+        <v>41</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="E2" s="1">
-        <v>2000</v>
+        <v>47</v>
+      </c>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>3</v>
+        <v>41</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E3" s="1">
-        <v>1500</v>
+        <v>47</v>
+      </c>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>3</v>
+        <v>41</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>12</v>
+        <v>42</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>13</v>
+        <v>49</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>8</v>
+        <v>52</v>
       </c>
       <c r="E4" s="1">
-        <v>2800</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>3</v>
+        <v>41</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>12</v>
+        <v>42</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>11</v>
+        <v>50</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>8</v>
+        <v>51</v>
       </c>
       <c r="E5" s="1">
-        <v>3300</v>
+        <v>1700</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>3</v>
+        <v>41</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>7</v>
+        <v>42</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>10</v>
+        <v>43</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="E6" s="1">
-        <v>800</v>
+        <v>6800</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>3</v>
+        <v>41</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>9</v>
+        <v>45</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>8</v>
+        <v>46</v>
       </c>
       <c r="E7" s="1">
-        <v>1000</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
@@ -605,16 +676,16 @@
         <v>3</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>0</v>
       </c>
       <c r="E8" s="1">
-        <v>1200</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
@@ -622,16 +693,16 @@
         <v>3</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="E9" s="1">
-        <v>400</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
@@ -639,16 +710,16 @@
         <v>3</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E10" s="1">
-        <v>800</v>
+        <v>2800</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
@@ -656,16 +727,16 @@
         <v>3</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E11" s="1">
-        <v>1400</v>
+        <v>3300</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
@@ -673,49 +744,321 @@
         <v>3</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>0</v>
       </c>
       <c r="E12" s="1">
-        <v>1000</v>
+        <v>800</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E13" s="1">
-        <v>4000</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E14" s="1">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E15" s="1">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E16" s="1">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E17" s="1">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E18" s="1">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E19" s="1">
+        <v>1800</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E20" s="1">
+        <v>1700</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E21" s="1">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E22" s="1">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E23" s="1">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E24" s="1">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E25" s="1">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E26" s="1">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E27" s="1">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E28" s="1">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B14" s="1" t="s">
+      <c r="B29" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E29" s="1">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B30" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C14" s="1" t="s">
+      <c r="C30" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D14" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="E14" s="1">
+      <c r="D30" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E30" s="1">
         <v>5900</v>
       </c>
     </row>

--- a/data/accessories.xlsx
+++ b/data/accessories.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Pictures\accesories\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Downloads\home\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{071F2EF7-F4A2-4D56-898E-6296D0CFA43B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7506597-0819-4D2B-947F-B864A0E6E22C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2411" uniqueCount="828">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2412" uniqueCount="828">
   <si>
     <t>Product Type</t>
   </si>
@@ -2568,6 +2568,20 @@
   </cellStyles>
   <dxfs count="3">
     <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
       <font>
         <b/>
         <i val="0"/>
@@ -2595,20 +2609,6 @@
         <bottom/>
       </border>
     </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-      </border>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -2623,7 +2623,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{12AC1D06-4C66-4EC0-B744-3DDE1636CE20}" name="Table1" displayName="Table1" ref="A1:F733" totalsRowShown="0" headerRowDxfId="0" headerRowBorderDxfId="1" tableBorderDxfId="2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{12AC1D06-4C66-4EC0-B744-3DDE1636CE20}" name="Table1" displayName="Table1" ref="A1:F733" totalsRowShown="0" headerRowDxfId="2" headerRowBorderDxfId="1" tableBorderDxfId="0">
   <autoFilter ref="A1:F733" xr:uid="{12AC1D06-4C66-4EC0-B744-3DDE1636CE20}"/>
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{C576B02F-5B16-4341-8AFB-F09023552B90}" name="Product Type"/>
@@ -2958,7 +2958,7 @@
       <c r="C2" t="s">
         <v>826</v>
       </c>
-      <c r="F2" t="s">
+      <c r="E2" t="s">
         <v>827</v>
       </c>
     </row>
@@ -8203,6 +8203,9 @@
       <c r="C410" t="s">
         <v>826</v>
       </c>
+      <c r="E410" t="s">
+        <v>827</v>
+      </c>
       <c r="F410" t="s">
         <v>827</v>
       </c>
@@ -9323,7 +9326,7 @@
         <v>1390</v>
       </c>
     </row>
-    <row r="481" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="481" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A481" t="s">
         <v>479</v>
       </c>
@@ -9340,7 +9343,7 @@
         <v>2090</v>
       </c>
     </row>
-    <row r="482" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="482" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A482" t="s">
         <v>479</v>
       </c>
@@ -9354,7 +9357,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="483" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="483" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A483" t="s">
         <v>479</v>
       </c>
@@ -9368,7 +9371,7 @@
         <v>910</v>
       </c>
     </row>
-    <row r="484" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="484" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A484" t="s">
         <v>479</v>
       </c>
@@ -9382,7 +9385,7 @@
         <v>1120</v>
       </c>
     </row>
-    <row r="488" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="488" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A488" t="s">
         <v>499</v>
       </c>
@@ -9392,11 +9395,11 @@
       <c r="C488" t="s">
         <v>826</v>
       </c>
-      <c r="F488" t="s">
+      <c r="E488" t="s">
         <v>827</v>
       </c>
     </row>
-    <row r="489" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="489" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A489" t="s">
         <v>499</v>
       </c>
@@ -9413,7 +9416,7 @@
         <v>5790</v>
       </c>
     </row>
-    <row r="490" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="490" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A490" t="s">
         <v>499</v>
       </c>
@@ -9430,7 +9433,7 @@
         <v>4430</v>
       </c>
     </row>
-    <row r="491" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="491" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A491" t="s">
         <v>499</v>
       </c>
@@ -9447,7 +9450,7 @@
         <v>5790</v>
       </c>
     </row>
-    <row r="492" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="492" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A492" t="s">
         <v>499</v>
       </c>
@@ -9464,7 +9467,7 @@
         <v>6095</v>
       </c>
     </row>
-    <row r="493" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="493" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A493" t="s">
         <v>499</v>
       </c>
@@ -9481,7 +9484,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="494" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="494" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A494" t="s">
         <v>499</v>
       </c>
@@ -9498,7 +9501,7 @@
         <v>1370</v>
       </c>
     </row>
-    <row r="495" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="495" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A495" t="s">
         <v>499</v>
       </c>
@@ -9508,11 +9511,11 @@
       <c r="C495" t="s">
         <v>826</v>
       </c>
-      <c r="F495" t="s">
+      <c r="E495" t="s">
         <v>827</v>
       </c>
     </row>
-    <row r="496" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="496" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A496" t="s">
         <v>511</v>
       </c>
@@ -10608,7 +10611,7 @@
         <v>1970</v>
       </c>
     </row>
-    <row r="561" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="561" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A561" t="s">
         <v>511</v>
       </c>
@@ -10625,7 +10628,7 @@
         <v>1880</v>
       </c>
     </row>
-    <row r="562" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="562" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A562" t="s">
         <v>511</v>
       </c>
@@ -10642,7 +10645,7 @@
         <v>1665</v>
       </c>
     </row>
-    <row r="563" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="563" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A563" t="s">
         <v>511</v>
       </c>
@@ -10659,7 +10662,7 @@
         <v>1230</v>
       </c>
     </row>
-    <row r="564" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="564" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A564" t="s">
         <v>511</v>
       </c>
@@ -10676,7 +10679,7 @@
         <v>990</v>
       </c>
     </row>
-    <row r="567" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="567" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A567" t="s">
         <v>598</v>
       </c>
@@ -10686,11 +10689,11 @@
       <c r="C567" t="s">
         <v>826</v>
       </c>
-      <c r="F567" t="s">
+      <c r="E567" t="s">
         <v>827</v>
       </c>
     </row>
-    <row r="568" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="568" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A568" t="s">
         <v>598</v>
       </c>
@@ -10707,7 +10710,7 @@
         <v>5395</v>
       </c>
     </row>
-    <row r="569" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="569" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A569" t="s">
         <v>598</v>
       </c>
@@ -10724,7 +10727,7 @@
         <v>3100</v>
       </c>
     </row>
-    <row r="570" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="570" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A570" t="s">
         <v>598</v>
       </c>
@@ -10741,7 +10744,7 @@
         <v>1475</v>
       </c>
     </row>
-    <row r="571" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="571" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A571" t="s">
         <v>598</v>
       </c>
@@ -10758,7 +10761,7 @@
         <v>1540</v>
       </c>
     </row>
-    <row r="572" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="572" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A572" t="s">
         <v>598</v>
       </c>
@@ -10775,7 +10778,7 @@
         <v>1770</v>
       </c>
     </row>
-    <row r="573" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="573" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A573" t="s">
         <v>598</v>
       </c>
@@ -10792,7 +10795,7 @@
         <v>1735</v>
       </c>
     </row>
-    <row r="574" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="574" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A574" t="s">
         <v>598</v>
       </c>
@@ -10809,7 +10812,7 @@
         <v>2100</v>
       </c>
     </row>
-    <row r="575" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="575" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A575" t="s">
         <v>598</v>
       </c>
@@ -10826,7 +10829,7 @@
         <v>2400</v>
       </c>
     </row>
-    <row r="576" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="576" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A576" t="s">
         <v>598</v>
       </c>
@@ -11931,7 +11934,7 @@
         <v>4415</v>
       </c>
     </row>
-    <row r="641" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="641" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A641" t="s">
         <v>598</v>
       </c>
@@ -11948,7 +11951,7 @@
         <v>2330</v>
       </c>
     </row>
-    <row r="642" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="642" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A642" t="s">
         <v>598</v>
       </c>
@@ -11965,7 +11968,7 @@
         <v>2140</v>
       </c>
     </row>
-    <row r="643" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="643" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A643" t="s">
         <v>598</v>
       </c>
@@ -11982,7 +11985,7 @@
         <v>2610</v>
       </c>
     </row>
-    <row r="644" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="644" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A644" t="s">
         <v>598</v>
       </c>
@@ -11999,7 +12002,7 @@
         <v>2605</v>
       </c>
     </row>
-    <row r="645" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="645" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A645" t="s">
         <v>598</v>
       </c>
@@ -12016,7 +12019,7 @@
         <v>3750</v>
       </c>
     </row>
-    <row r="646" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="646" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A646" t="s">
         <v>598</v>
       </c>
@@ -12033,7 +12036,7 @@
         <v>3350</v>
       </c>
     </row>
-    <row r="647" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="647" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A647" t="s">
         <v>598</v>
       </c>
@@ -12050,7 +12053,7 @@
         <v>3850</v>
       </c>
     </row>
-    <row r="648" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="648" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A648" t="s">
         <v>598</v>
       </c>
@@ -12067,7 +12070,7 @@
         <v>4750</v>
       </c>
     </row>
-    <row r="649" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="649" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A649" t="s">
         <v>598</v>
       </c>
@@ -12084,7 +12087,7 @@
         <v>3050</v>
       </c>
     </row>
-    <row r="650" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="650" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A650" t="s">
         <v>598</v>
       </c>
@@ -12094,7 +12097,7 @@
       <c r="C650" t="s">
         <v>826</v>
       </c>
-      <c r="F650" t="s">
+      <c r="E650" t="s">
         <v>827</v>
       </c>
     </row>
